--- a/data/trans_bre/IP11A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11A_R-Habitat-trans_bre.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,39</t>
+          <t>0,0; 52,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,82</t>
+          <t>17,94</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>150,53%</t>
+          <t>182,92%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,3</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,55</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 64,25</t>
+          <t>-11,39; 61,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-12,21</t>
+          <t>-13,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 0,0</t>
+          <t>-30,55; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 0,0</t>
+          <t>-16,94; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 0,0</t>
+          <t>-31,6; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 0,0</t>
+          <t>-55,98; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 0,0</t>
+          <t>-40,74; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 0,0</t>
+          <t>-31,03; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 76,65</t>
+          <t>-12,25; 75,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -1,05</t>
+          <t>-10,17; -1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,85</t>
+          <t>-7,83; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 22,24</t>
+          <t>-0,95; 23,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 16,62</t>
+          <t>-12,68; 14,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">

--- a/data/trans_bre/IP11A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP11A_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,149 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>19.13605203892187</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 52,3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>52.29934097846664</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,94</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,58</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,39; 61,93</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.311026695805199</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.148840249935895</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>17.94495099837741</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.82919745464913</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.39250230527471</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-30,55; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-16,94; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-31,6; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-55,98; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>17.79382829942019</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>29.57975356777545</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>61.93317596176595</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +769,245 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-12,53</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-9,77</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20,07</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>331,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.47775833073987</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.46319428869281</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-7.449110075341549</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-13.18317980335658</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-40,74; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-31,03; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-12,25; 75,82</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-30.54582363629452</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-16.93811450332127</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-31.60311572809857</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-55.98480813618405</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-12.52750038173296</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-9.770106149126095</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20.06846822671019</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>3.311861601307077</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-40.73968116702093</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-31.03107066951559</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-12.24691892460531</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>75.82244494227002</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,92</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-60,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>268,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,17; -1,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 1,9</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 23,1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,68; 14,48</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-3.924282862507225</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.063225483186605</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8.575565336622015</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.4571682713843644</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.6005719536694191</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>2.684238393858046</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.06533613399624691</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.16517298405313</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.829106493936414</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.952416412303002</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-12.68198483074668</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-1.049077532841135</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.903841397796948</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>23.10009575095915</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>14.48144189573562</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1015,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
